--- a/survey_templates/043_pet_sitter_feedback_form--survey_templates.xlsx
+++ b/survey_templates/043_pet_sitter_feedback_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'unacceptable'}</t>
+          <t>unacceptable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Unacceptable'}</t>
+          <t>Unacceptable</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'unacceptable'}</t>
+          <t>unacceptable</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Unacceptable'}</t>
+          <t>Unacceptable</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'almost_always_available'}</t>
+          <t>almost_always_available</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Almost always available'}</t>
+          <t>Almost always available</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_available'}</t>
+          <t>sometimes_available</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes available'}</t>
+          <t>Sometimes available</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_available'}</t>
+          <t>rarely_available</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely available'}</t>
+          <t>Rarely available</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'almost_always_available'}</t>
+          <t>almost_always_available</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Almost always available'}</t>
+          <t>Almost always available</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_available'}</t>
+          <t>sometimes_available</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes available'}</t>
+          <t>Sometimes available</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_available'}</t>
+          <t>rarely_available</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely available'}</t>
+          <t>Rarely available</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'always_responsive'}</t>
+          <t>always_responsive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Always responsive'}</t>
+          <t>Always responsive</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'often_responsive'}</t>
+          <t>often_responsive</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Often responsive'}</t>
+          <t>Often responsive</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally_responsive'}</t>
+          <t>occasionally_responsive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally responsive'}</t>
+          <t>Occasionally responsive</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_responsive'}</t>
+          <t>rarely_responsive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely responsive'}</t>
+          <t>Rarely responsive</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'unacceptable'}</t>
+          <t>unacceptable</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Unacceptable'}</t>
+          <t>Unacceptable</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'always_available'}</t>
+          <t>always_available</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Always available'}</t>
+          <t>Always available</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'often_available'}</t>
+          <t>often_available</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Often available'}</t>
+          <t>Often available</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_available'}</t>
+          <t>sometimes_available</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes available'}</t>
+          <t>Sometimes available</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_available'}</t>
+          <t>rarely_available</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely available'}</t>
+          <t>Rarely available</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
